--- a/outputs/etf_trend_strategy/threshold_0.9/backtests/window_15/return_vol/post_rank_positive_return_rsi_bias_filter/staggered_10d/rsi_10_gt_60__bias_15_gt_-0.02/next_day_vwap/next_day_vwap_backtest_metrics.xlsx
+++ b/outputs/etf_trend_strategy/threshold_0.9/backtests/window_15/return_vol/post_rank_positive_return_rsi_bias_filter/staggered_10d/rsi_10_gt_60__bias_15_gt_-0.02/next_day_vwap/next_day_vwap_backtest_metrics.xlsx
@@ -563,7 +563,7 @@
         </is>
       </c>
       <c r="C5" s="4" t="n">
-        <v>1.125499489398303</v>
+        <v>0.8342354342026506</v>
       </c>
     </row>
     <row r="6">
@@ -578,7 +578,7 @@
         </is>
       </c>
       <c r="C6" s="5" t="n">
-        <v>0.1254994893983088</v>
+        <v>-0.1657645657973426</v>
       </c>
     </row>
     <row r="7">
@@ -593,7 +593,7 @@
         </is>
       </c>
       <c r="C7" s="5" t="n">
-        <v>0.02265367553525843</v>
+        <v>-0.03375720789224068</v>
       </c>
     </row>
     <row r="8">
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="C9" s="5" t="n">
-        <v>0.04016160941789404</v>
+        <v>-0.01721503401314894</v>
       </c>
     </row>
     <row r="10">
@@ -638,7 +638,7 @@
         </is>
       </c>
       <c r="C10" s="5" t="n">
-        <v>0.2457649895114897</v>
+        <v>0.2008534414907008</v>
       </c>
     </row>
     <row r="11">
@@ -653,7 +653,7 @@
         </is>
       </c>
       <c r="C11" s="4" t="n">
-        <v>0.1536511530975047</v>
+        <v>-0.1444420108190528</v>
       </c>
     </row>
     <row r="12">
@@ -668,7 +668,7 @@
         </is>
       </c>
       <c r="C12" s="4" t="n">
-        <v>0.2179340115189715</v>
+        <v>-0.1996313747722722</v>
       </c>
     </row>
     <row r="13">
@@ -683,7 +683,7 @@
         </is>
       </c>
       <c r="C13" s="5" t="n">
-        <v>0.3774032245207947</v>
+        <v>0.4683955057662896</v>
       </c>
     </row>
     <row r="14">
@@ -699,7 +699,7 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>2021年09月-2025年06月</t>
+          <t>2021年09月-2024年09月</t>
         </is>
       </c>
     </row>
@@ -715,7 +715,7 @@
         </is>
       </c>
       <c r="C15" s="4" t="n">
-        <v>0.06002512449124618</v>
+        <v>-0.07206987999813166</v>
       </c>
     </row>
     <row r="16">
@@ -730,7 +730,7 @@
         </is>
       </c>
       <c r="C16" s="5" t="n">
-        <v>0.2028376733690947</v>
+        <v>0.1795657810967279</v>
       </c>
     </row>
     <row r="17">
@@ -745,7 +745,7 @@
         </is>
       </c>
       <c r="C17" s="4" t="n">
-        <v>0.2529806010831926</v>
+        <v>-0.08609520351053232</v>
       </c>
     </row>
     <row r="18">
@@ -760,7 +760,7 @@
         </is>
       </c>
       <c r="C18" s="5" t="n">
-        <v>0.3324264590337254</v>
+        <v>0.3617795417276926</v>
       </c>
     </row>
     <row r="19">
@@ -776,7 +776,7 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>2024年02月-2025年06月</t>
+          <t>2021年09月-2025年10月</t>
         </is>
       </c>
     </row>
@@ -792,7 +792,7 @@
         </is>
       </c>
       <c r="C20" s="6" t="n">
-        <v>18.71668847023485</v>
+        <v>13.38746701625879</v>
       </c>
     </row>
     <row r="21">
@@ -807,7 +807,7 @@
         </is>
       </c>
       <c r="C21" s="5" t="n">
-        <v>0.07483524430439023</v>
+        <v>0.0535273302417754</v>
       </c>
     </row>
     <row r="22">
@@ -822,7 +822,7 @@
         </is>
       </c>
       <c r="C22" s="5" t="n">
-        <v>0.1800986302484884</v>
+        <v>0.132647663433766</v>
       </c>
     </row>
     <row r="23">
@@ -837,7 +837,7 @@
         </is>
       </c>
       <c r="C23" s="7" t="n">
-        <v>3.211278195488722</v>
+        <v>3.619548872180451</v>
       </c>
     </row>
     <row r="24">
@@ -1034,7 +1034,7 @@
         </is>
       </c>
       <c r="C9" s="5" t="n">
-        <v>0.01</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="10">
